--- a/rafa-arevalo/a12-ia-no-financeiro-contas-a-pagar/historico-pedidos-lumina.xlsx
+++ b/rafa-arevalo/a12-ia-no-financeiro-contas-a-pagar/historico-pedidos-lumina.xlsx
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>10500</v>
+        <v>12020</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
